--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-09T00:29:45+00:00</t>
+          <t>2026-05-10T00:27:05+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-10T00:27:05+00:00</t>
+          <t>2026-05-11T00:27:32+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-11T00:27:32+00:00</t>
+          <t>2026-05-12T00:28:01+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-12T00:28:01+00:00</t>
+          <t>2026-05-13T00:30:33+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-13T00:30:33+00:00</t>
+          <t>2026-05-14T00:31:30+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-14T00:31:30+00:00</t>
+          <t>2026-05-15T00:29:08+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-15T00:29:08+00:00</t>
+          <t>2026-05-16T00:27:46+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-16T00:27:46+00:00</t>
+          <t>2026-05-17T00:28:39+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-17T00:28:39+00:00</t>
+          <t>2026-05-18T00:29:13+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-18T00:29:13+00:00</t>
+          <t>2026-05-19T00:32:39+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-19T00:32:39+00:00</t>
+          <t>2026-05-20T00:34:14+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-20T00:34:14+00:00</t>
+          <t>2026-05-21T00:35:02+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-21T00:35:02+00:00</t>
+          <t>2026-05-22T00:32:22+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-22T00:32:22+00:00</t>
+          <t>2026-05-23T00:33:12+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-23T00:33:12+00:00</t>
+          <t>2026-05-24T00:31:49+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-24T00:31:49+00:00</t>
+          <t>2026-05-25T00:34:08+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-25T00:34:08+00:00</t>
+          <t>2026-05-26T00:33:53+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-26T00:33:53+00:00</t>
+          <t>2026-05-27T00:33:47+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-27T00:33:47+00:00</t>
+          <t>2026-05-28T00:30:18+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-28T00:30:18+00:00</t>
+          <t>2026-05-29T00:36:26+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-29T00:36:26+00:00</t>
+          <t>2026-05-30T00:32:53+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-30T00:32:53+00:00</t>
+          <t>2026-05-31T00:34:07+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-31T00:34:07+00:00</t>
+          <t>2026-06-01T00:36:45+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-01T00:36:45+00:00</t>
+          <t>2026-06-02T00:40:31+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-02T00:40:31+00:00</t>
+          <t>2026-06-03T00:45:33+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-03T00:45:33+00:00</t>
+          <t>2026-06-04T00:43:31+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-04T00:43:31+00:00</t>
+          <t>2026-06-05T00:36:44+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-05T00:36:44+00:00</t>
+          <t>2026-06-06T00:34:43+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-06T00:34:43+00:00</t>
+          <t>2026-06-07T00:35:40+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-07T00:35:40+00:00</t>
+          <t>2026-06-08T00:37:15+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-08T00:37:15+00:00</t>
+          <t>2026-06-09T00:32:24+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-09T00:32:24+00:00</t>
+          <t>2026-06-10T00:38:19+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-10T00:38:19+00:00</t>
+          <t>2026-06-11T00:42:33+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-11T00:42:33+00:00</t>
+          <t>2026-06-12T00:47:28+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-12T00:47:28+00:00</t>
+          <t>2026-06-13T00:39:20+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-13T00:39:20+00:00</t>
+          <t>2026-06-14T00:37:58+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-14T00:37:58+00:00</t>
+          <t>2026-06-15T00:39:20+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-15T00:39:20+00:00</t>
+          <t>2026-06-16T00:49:56+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-16T00:49:56+00:00</t>
+          <t>2026-06-17T00:39:56+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-17T00:39:56+00:00</t>
+          <t>2026-06-18T00:44:00+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-18T00:44:00+00:00</t>
+          <t>2026-06-19T00:44:00+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-19T00:44:00+00:00</t>
+          <t>2026-06-20T00:36:11+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-20T00:36:11+00:00</t>
+          <t>2026-06-21T00:39:14+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-21T00:39:14+00:00</t>
+          <t>2026-06-22T00:38:15+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-22T00:38:15+00:00</t>
+          <t>2026-06-23T00:36:10+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-23T00:36:10+00:00</t>
+          <t>2026-06-24T00:30:28+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-24T00:30:28+00:00</t>
+          <t>2026-06-25T00:35:29+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-25T00:35:29+00:00</t>
+          <t>2026-06-26T00:41:48+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-26T00:41:48+00:00</t>
+          <t>2026-06-27T00:33:14+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-27T00:33:14+00:00</t>
+          <t>2026-06-28T00:33:10+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-28T00:33:10+00:00</t>
+          <t>2026-06-29T00:35:20+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-29T00:35:20+00:00</t>
+          <t>2026-06-30T00:33:47+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-30T00:33:47+00:00</t>
+          <t>2026-07-01T00:38:33+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-01T00:38:33+00:00</t>
+          <t>2026-07-02T00:33:37+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-02T00:33:37+00:00</t>
+          <t>2026-07-03T02:05:47+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-03T02:05:47+00:00</t>
+          <t>2026-07-04T02:03:18+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-04T02:03:18+00:00</t>
+          <t>2026-07-05T02:11:17+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-05T02:11:17+00:00</t>
+          <t>2026-07-06T02:16:12+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-06T02:16:12+00:00</t>
+          <t>2026-07-07T02:11:30+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-07T02:11:30+00:00</t>
+          <t>2026-07-08T01:53:06+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-08T01:53:06+00:00</t>
+          <t>2026-07-09T02:06:08+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-09T02:06:08+00:00</t>
+          <t>2026-07-10T02:04:41+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-10T02:04:41+00:00</t>
+          <t>2026-07-11T01:51:19+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-11T01:51:19+00:00</t>
+          <t>2026-07-12T01:54:04+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-12T01:54:04+00:00</t>
+          <t>2026-07-13T01:56:41+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-13T01:56:41+00:00</t>
+          <t>2026-07-14T01:43:45+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-14T01:43:45+00:00</t>
+          <t>2026-07-15T01:29:22+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-15T01:29:22+00:00</t>
+          <t>2026-07-16T01:49:58+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-16T01:49:58+00:00</t>
+          <t>2026-07-17T01:53:27+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-17T01:53:27+00:00</t>
+          <t>2026-07-18T01:43:58+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-18T01:43:58+00:00</t>
+          <t>2026-07-19T01:52:02+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-19T01:52:02+00:00</t>
+          <t>2026-07-20T03:25:55+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-20T03:25:55+00:00</t>
+          <t>2026-07-21T01:55:40+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-21T01:55:40+00:00</t>
+          <t>2026-07-22T01:50:55+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-22T01:50:55+00:00</t>
+          <t>2026-07-23T01:59:36+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-23T01:59:36+00:00</t>
+          <t>2026-07-24T01:54:55+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-24T01:54:55+00:00</t>
+          <t>2026-07-25T01:53:33+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-25T01:53:33+00:00</t>
+          <t>2026-07-26T01:57:18+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-26T01:57:18+00:00</t>
+          <t>2026-07-27T02:07:45+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-27T02:07:45+00:00</t>
+          <t>2026-07-28T01:47:16+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-28T01:47:16+00:00</t>
+          <t>2026-07-29T01:49:05+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-29T01:49:05+00:00</t>
+          <t>2026-07-30T01:32:38+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-30T01:32:38+00:00</t>
+          <t>2026-07-31T01:58:46+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-31T01:58:46+00:00</t>
+          <t>2026-08-01T02:00:59+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-01T02:00:59+00:00</t>
+          <t>2026-08-02T01:55:09+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-02T01:55:09+00:00</t>
+          <t>2026-08-03T01:57:50+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-03T01:57:50+00:00</t>
+          <t>2026-08-04T01:44:56+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-04T01:44:56+00:00</t>
+          <t>2026-08-05T01:46:10+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-05T01:46:10+00:00</t>
+          <t>2026-08-06T01:46:37+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-06T01:46:37+00:00</t>
+          <t>2026-08-07T02:11:05+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-07T02:11:05+00:00</t>
+          <t>2026-08-08T00:58:03+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-08T00:58:03+00:00</t>
+          <t>2026-08-09T01:02:17+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-09T01:02:17+00:00</t>
+          <t>2026-08-10T01:04:28+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-10T01:04:28+00:00</t>
+          <t>2026-08-11T01:02:48+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-11T01:02:48+00:00</t>
+          <t>2026-08-12T01:10:14+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-12T01:10:14+00:00</t>
+          <t>2026-08-13T01:12:40+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-13T01:12:40+00:00</t>
+          <t>2026-08-14T01:10:36+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-14T01:10:36+00:00</t>
+          <t>2026-08-15T00:44:12+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-15T00:44:12+00:00</t>
+          <t>2026-08-16T00:45:08+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-16T00:45:08+00:00</t>
+          <t>2026-08-17T00:43:25+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-17T00:43:25+00:00</t>
+          <t>2026-08-17T06:43:39+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-17T06:43:39+00:00</t>
+          <t>2026-08-17T06:55:53+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-17T06:55:53+00:00</t>
+          <t>2026-08-17T07:43:20+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-17T07:43:20+00:00</t>
+          <t>2026-08-17T08:00:50+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-17T08:00:50+00:00</t>
+          <t>2026-08-17T08:14:15+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-17T08:14:15+00:00</t>
+          <t>2026-08-17T08:29:33+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-17T08:29:33+00:00</t>
+          <t>2026-08-17T09:21:51+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-17T09:21:51+00:00</t>
+          <t>2026-08-17T09:27:17+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-17T09:27:17+00:00</t>
+          <t>2026-08-17T10:45:57+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-17T10:45:57+00:00</t>
+          <t>2026-08-17T12:52:25+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-17T12:52:25+00:00</t>
+          <t>2026-08-17T23:14:56+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-17T23:14:56+00:00</t>
+          <t>2026-08-18T05:53:25+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-18T05:53:25+00:00</t>
+          <t>2026-08-18T23:15:06+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-18T23:15:06+00:00</t>
+          <t>2026-08-19T23:15:47+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-19T23:15:47+00:00</t>
+          <t>2026-08-20T23:18:22+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-20T23:18:22+00:00</t>
+          <t>2026-08-21T23:15:50+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-21T23:15:50+00:00</t>
+          <t>2026-08-22T23:13:42+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-22T23:13:42+00:00</t>
+          <t>2026-08-23T23:13:14+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-23T23:13:14+00:00</t>
+          <t>2026-08-24T23:16:21+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-24T23:16:21+00:00</t>
+          <t>2026-08-25T23:18:10+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-25T23:18:10+00:00</t>
+          <t>2026-08-27T04:10:16+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-27T04:10:16+00:00</t>
+          <t>2026-08-28T06:26:52+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-28T06:26:52+00:00</t>
+          <t>2026-08-29T03:59:09+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-29T03:59:09+00:00</t>
+          <t>2026-08-30T00:56:42+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-30T00:56:42+00:00</t>
+          <t>2026-08-31T01:01:22+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-31T01:01:22+00:00</t>
+          <t>2026-09-01T01:31:52+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-01T01:31:52+00:00</t>
+          <t>2026-09-02T00:41:47+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-02T00:41:47+00:00</t>
+          <t>2026-09-03T00:53:37+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-03T00:53:37+00:00</t>
+          <t>2026-09-04T00:33:47+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-04T00:33:47+00:00</t>
+          <t>2026-09-05T00:31:22+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-05T00:31:22+00:00</t>
+          <t>2026-09-06T00:24:15+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-06T00:24:15+00:00</t>
+          <t>2026-09-07T00:31:31+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-07T00:31:31+00:00</t>
+          <t>2026-09-07T07:49:50+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-07T07:49:50+00:00</t>
+          <t>2026-09-07T09:43:22+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-07T09:43:22+00:00</t>
+          <t>2026-09-07T11:03:01+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-07T11:03:01+00:00</t>
+          <t>2026-09-08T00:50:21+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-08T00:50:21+00:00</t>
+          <t>2026-09-09T00:54:10+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-09T00:54:10+00:00</t>
+          <t>2026-09-09T01:45:43+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-09T01:45:43+00:00</t>
+          <t>2026-09-09T02:38:41+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-09T02:38:41+00:00</t>
+          <t>2026-09-10T00:44:20+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-10T00:44:20+00:00</t>
+          <t>2026-09-11T00:42:37+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-11T00:42:37+00:00</t>
+          <t>2026-09-12T00:50:30+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/basel-aml-index.xlsx
+++ b/public/downloads/basel-aml-index.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-12T00:50:30+00:00</t>
+          <t>2026-09-13T00:31:13+00:00</t>
         </is>
       </c>
     </row>
